--- a/results/ALL_EXPERIMENTS_BY_MODEL_AUDITED.xlsx
+++ b/results/ALL_EXPERIMENTS_BY_MODEL_AUDITED.xlsx
@@ -17428,7 +17428,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>**Thinking Process:**\n\n (10 tokens)</t>
+          <t>Dynamic Teacher Constraint-OFF Prefixes (51 unique task-specific prefixes, k=10 tokens; e.g. "**Thinking Process:**\n\n")</t>
         </is>
       </c>
     </row>
@@ -18243,7 +18243,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>**Acknowledging the user's constraints and instructions**\n\n (10 tokens)</t>
+          <t>Dynamic Teacher Constraint-ON Prefixes (188 unique task-specific prefixes, k=10 tokens; teacher-steered constraint acknowledgment)</t>
         </is>
       </c>
     </row>
@@ -28939,7 +28939,7 @@
         <v>0.1166666666666666</v>
       </c>
       <c r="H7" s="44" t="n">
-        <v>4401.686666666666</v>
+        <v>4401.69</v>
       </c>
       <c r="I7" s="43" t="n">
         <v>0</v>
@@ -28948,16 +28948,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="43" t="n">
-        <v>0.4230769230769231</v>
+        <v>0.4231</v>
       </c>
       <c r="L7" s="43" t="n">
-        <v>0.0566037735849056</v>
+        <v>0.0566</v>
       </c>
       <c r="M7" s="43" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1071</v>
       </c>
       <c r="N7" s="43" t="n">
-        <v>0.2244897959183673</v>
+        <v>0.2245</v>
       </c>
     </row>
     <row r="8">
@@ -28998,16 +28998,16 @@
         <v>0</v>
       </c>
       <c r="K8" s="39" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2692</v>
       </c>
       <c r="L8" s="39" t="n">
-        <v>0.1886792452830188</v>
+        <v>0.1887</v>
       </c>
       <c r="M8" s="39" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4286</v>
       </c>
       <c r="N8" s="39" t="n">
-        <v>0.3469387755102041</v>
+        <v>0.3469</v>
       </c>
     </row>
     <row r="9">
@@ -29048,16 +29048,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="43" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2692</v>
       </c>
       <c r="L9" s="43" t="n">
-        <v>0.4339622641509434</v>
+        <v>0.3962</v>
       </c>
       <c r="M9" s="43" t="n">
-        <v>0.4821428571428571</v>
+        <v>0.4821</v>
       </c>
       <c r="N9" s="43" t="n">
-        <v>0.6530612244897959</v>
+        <v>0.6531</v>
       </c>
     </row>
     <row r="10">
@@ -29098,16 +29098,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="50" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5769</v>
       </c>
       <c r="L10" s="50" t="n">
-        <v>0.6226415094339622</v>
+        <v>0.6226</v>
       </c>
       <c r="M10" s="50" t="n">
         <v>0.5</v>
       </c>
       <c r="N10" s="50" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7143</v>
       </c>
     </row>
     <row r="11">
@@ -29139,25 +29139,25 @@
         <v>0.2066666666666666</v>
       </c>
       <c r="H11" s="44" t="n">
-        <v>0.86</v>
+        <v>2023.71</v>
       </c>
       <c r="I11" s="43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J11" s="43" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K11" s="43" t="n">
-        <v>43</v>
+        <v>0.5769</v>
       </c>
       <c r="L11" s="43" t="n">
-        <v>53</v>
+        <v>0.4906</v>
       </c>
       <c r="M11" s="43" t="n">
-        <v>47</v>
+        <v>0.375</v>
       </c>
       <c r="N11" s="43" t="n">
-        <v>49</v>
+        <v>0.4694</v>
       </c>
     </row>
     <row r="12">
@@ -29189,25 +29189,25 @@
         <v>0.1433333333333333</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>0.8133333333333334</v>
+        <v>3395.06</v>
       </c>
       <c r="I12" s="39" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J12" s="39" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K12" s="39" t="n">
-        <v>43</v>
+        <v>0.6538</v>
       </c>
       <c r="L12" s="39" t="n">
-        <v>53</v>
+        <v>0.1132</v>
       </c>
       <c r="M12" s="39" t="n">
-        <v>47</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="N12" s="39" t="n">
-        <v>49</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="13">
@@ -29239,25 +29239,25 @@
         <v>0.0966666666666666</v>
       </c>
       <c r="H13" s="44" t="n">
-        <v>0.7966666666666666</v>
+        <v>3514.99</v>
       </c>
       <c r="I13" s="43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J13" s="43" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K13" s="43" t="n">
-        <v>43</v>
+        <v>0.4231</v>
       </c>
       <c r="L13" s="43" t="n">
-        <v>53</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="M13" s="43" t="n">
-        <v>47</v>
+        <v>0.0536</v>
       </c>
       <c r="N13" s="43" t="n">
-        <v>49</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="14">
@@ -29289,25 +29289,25 @@
         <v>0.15</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>0.74</v>
+        <v>4638.24</v>
       </c>
       <c r="I14" s="39" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J14" s="39" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K14" s="39" t="n">
-        <v>43</v>
+        <v>0.3269</v>
       </c>
       <c r="L14" s="39" t="n">
-        <v>53</v>
+        <v>0.0566</v>
       </c>
       <c r="M14" s="39" t="n">
-        <v>47</v>
+        <v>0.3214</v>
       </c>
       <c r="N14" s="39" t="n">
-        <v>49</v>
+        <v>0.3265</v>
       </c>
     </row>
     <row r="15">
@@ -29339,25 +29339,25 @@
         <v>0.09</v>
       </c>
       <c r="H15" s="44" t="n">
-        <v>0.6366666666666667</v>
+        <v>4504.3</v>
       </c>
       <c r="I15" s="43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J15" s="43" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K15" s="43" t="n">
-        <v>43</v>
+        <v>0.3846</v>
       </c>
       <c r="L15" s="43" t="n">
-        <v>53</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="M15" s="43" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N15" s="43" t="n">
-        <v>49</v>
+        <v>0.1224</v>
       </c>
     </row>
     <row r="16">
@@ -29389,25 +29389,25 @@
         <v>0.0933333333333333</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>0.9266666666666666</v>
+        <v>263.34</v>
       </c>
       <c r="I16" s="39" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J16" s="39" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K16" s="39" t="n">
-        <v>43</v>
+        <v>0.2885</v>
       </c>
       <c r="L16" s="39" t="n">
-        <v>53</v>
+        <v>0.8113</v>
       </c>
       <c r="M16" s="39" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N16" s="39" t="n">
-        <v>49</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="17">
@@ -29439,25 +29439,25 @@
         <v>0.12</v>
       </c>
       <c r="H17" s="44" t="n">
-        <v>0.8333333333333334</v>
+        <v>799.3099999999999</v>
       </c>
       <c r="I17" s="43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J17" s="43" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K17" s="43" t="n">
-        <v>43</v>
+        <v>0.4231</v>
       </c>
       <c r="L17" s="43" t="n">
-        <v>53</v>
+        <v>0.4528</v>
       </c>
       <c r="M17" s="43" t="n">
-        <v>47</v>
+        <v>0.1964</v>
       </c>
       <c r="N17" s="43" t="n">
-        <v>49</v>
+        <v>0.3469</v>
       </c>
     </row>
     <row r="18">
@@ -29489,25 +29489,25 @@
         <v>0.1166666666666666</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>0.7433333333333333</v>
+        <v>4169.02</v>
       </c>
       <c r="I18" s="39" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J18" s="39" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K18" s="39" t="n">
-        <v>43</v>
+        <v>0.4231</v>
       </c>
       <c r="L18" s="39" t="n">
-        <v>53</v>
+        <v>0.0189</v>
       </c>
       <c r="M18" s="39" t="n">
-        <v>47</v>
+        <v>0.125</v>
       </c>
       <c r="N18" s="39" t="n">
-        <v>49</v>
+        <v>0.1633</v>
       </c>
     </row>
     <row r="19">
@@ -29539,25 +29539,25 @@
         <v>0</v>
       </c>
       <c r="H19" s="44" t="n">
-        <v>0.9633333333333334</v>
+        <v>754.49</v>
       </c>
       <c r="I19" s="43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J19" s="43" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K19" s="43" t="n">
-        <v>43</v>
+        <v>0.0192</v>
       </c>
       <c r="L19" s="43" t="n">
-        <v>53</v>
+        <v>0.0377</v>
       </c>
       <c r="M19" s="43" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N19" s="43" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -29589,25 +29589,25 @@
         <v>0.14</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>0.76</v>
+        <v>4210.87</v>
       </c>
       <c r="I20" s="39" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J20" s="39" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K20" s="39" t="n">
-        <v>43</v>
+        <v>0.4038</v>
       </c>
       <c r="L20" s="39" t="n">
-        <v>53</v>
+        <v>0.0377</v>
       </c>
       <c r="M20" s="39" t="n">
-        <v>47</v>
+        <v>0.2143</v>
       </c>
       <c r="N20" s="39" t="n">
-        <v>49</v>
+        <v>0.2041</v>
       </c>
     </row>
     <row r="21">
@@ -29639,25 +29639,25 @@
         <v>0.12</v>
       </c>
       <c r="H21" s="44" t="n">
-        <v>0.7266666666666667</v>
+        <v>4235.47</v>
       </c>
       <c r="I21" s="43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J21" s="43" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K21" s="43" t="n">
-        <v>43</v>
+        <v>0.3462</v>
       </c>
       <c r="L21" s="43" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M21" s="43" t="n">
-        <v>47</v>
+        <v>0.0536</v>
       </c>
       <c r="N21" s="43" t="n">
-        <v>49</v>
+        <v>0.4898</v>
       </c>
     </row>
     <row r="22">
@@ -29689,25 +29689,25 @@
         <v>0.0633333333333333</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>0.9366666666666666</v>
+        <v>3395.52</v>
       </c>
       <c r="I22" s="39" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J22" s="39" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K22" s="39" t="n">
-        <v>43</v>
+        <v>0.3654</v>
       </c>
       <c r="L22" s="39" t="n">
-        <v>53</v>
+        <v>0.0189</v>
       </c>
       <c r="M22" s="39" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="N22" s="39" t="n">
-        <v>49</v>
+        <v>0.08160000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -29739,25 +29739,25 @@
         <v>0.1266666666666666</v>
       </c>
       <c r="H23" s="44" t="n">
-        <v>0.8433333333333334</v>
+        <v>3569.3</v>
       </c>
       <c r="I23" s="43" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="J23" s="43" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K23" s="43" t="n">
-        <v>43</v>
+        <v>0.4231</v>
       </c>
       <c r="L23" s="43" t="n">
-        <v>53</v>
+        <v>0.4151</v>
       </c>
       <c r="M23" s="43" t="n">
-        <v>47</v>
+        <v>0.0893</v>
       </c>
       <c r="N23" s="43" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -29789,25 +29789,25 @@
         <v>0.16</v>
       </c>
       <c r="H24" s="40" t="n">
-        <v>0.8466666666666667</v>
+        <v>1405.63</v>
       </c>
       <c r="I24" s="39" t="n">
-        <v>56</v>
+        <v>0.0233</v>
       </c>
       <c r="J24" s="39" t="n">
-        <v>52</v>
+        <v>0.1277</v>
       </c>
       <c r="K24" s="39" t="n">
-        <v>43</v>
+        <v>0.6923</v>
       </c>
       <c r="L24" s="39" t="n">
-        <v>53</v>
+        <v>0.3208</v>
       </c>
       <c r="M24" s="39" t="n">
-        <v>47</v>
+        <v>0.1071</v>
       </c>
       <c r="N24" s="39" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29839,25 +29839,25 @@
         <v>0.18</v>
       </c>
       <c r="H25" s="44" t="n">
-        <v>2513.17</v>
+        <v>1866.35</v>
       </c>
       <c r="I25" s="43" t="n">
-        <v>0.02325581395348837</v>
+        <v>0.0233</v>
       </c>
       <c r="J25" s="43" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="43" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3077</v>
       </c>
       <c r="L25" s="43" t="n">
-        <v>0.4150943396226415</v>
+        <v>0.4151</v>
       </c>
       <c r="M25" s="43" t="n">
         <v>0.375</v>
       </c>
       <c r="N25" s="43" t="n">
-        <v>0.3877551020408163</v>
+        <v>0.3878</v>
       </c>
     </row>
   </sheetData>
